--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.44.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.44.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.44.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.44.xlsx
@@ -422,16 +422,16 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="40" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -593,24 +593,24 @@
       <c r="E2" s="1" t="inlineStr"/>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>L4: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR | candidate OCR token mismatch vs other OCR: "subpe" vs "subp" :: more than two years before the subpe Ã¦ na was issue</t>
+          <t>L4: candidate OCR token mismatch vs other OCR: "subpe" vs "subp" :: more than two years before the subpe æ na was issue</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr"/>
       <c r="H2" s="1" t="inlineStr"/>
       <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>L1: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: that any Defendant, against whom a Subp Ã¦ na to</t>
-        </is>
-      </c>
+      <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L71: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: arried on toâ€˜</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]37</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]37</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L28: isolated marker/symbol line :: 37</t>
@@ -618,7 +618,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L65: isolated marker/symbol line :: %</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]37</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>67</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -658,14 +658,10 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L4: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR | candidate OCR token mismatch vs other OCR: "subpe" vs "subp" :: more than two years before the subpe Ã¦ na was issue</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L79: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: : â€”</t>
+          <t>L83: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -677,7 +673,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L83: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L65: isolated marker/symbol line :: %</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -713,16 +709,8 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L15: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: n a Subp Ã¦ na to appear</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L83: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -730,7 +718,11 @@
           <t>L54: isolated marker/symbol line :: 2</t>
         </is>
       </c>
-      <c r="O4" s="1" t="inlineStr"/>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>L79: isolated marker/symbol line :: : —</t>
+        </is>
+      </c>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr"/>
@@ -750,7 +742,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -764,11 +756,7 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L18: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: bp Ã¦ na was issued, and</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
@@ -777,7 +765,11 @@
           <t>L64: isolated marker/symbol line :: 4</t>
         </is>
       </c>
-      <c r="O5" s="1" t="inlineStr"/>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>L83: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr"/>
       <c r="R5" s="1" t="inlineStr"/>
@@ -953,12 +945,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -997,7 +989,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1036,7 +1028,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
